--- a/content/action_results.xlsx
+++ b/content/action_results.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="98" uniqueCount="48">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="144" uniqueCount="62">
   <si>
     <t>结果id</t>
   </si>
@@ -34,6 +34,9 @@
     <t>金钱</t>
   </si>
   <si>
+    <t>粉丝</t>
+  </si>
+  <si>
     <t>演唱</t>
   </si>
   <si>
@@ -155,6 +158,45 @@
   </si>
   <si>
     <t>睡了一觉，感觉活过来了。</t>
+  </si>
+  <si>
+    <t>res-show-s</t>
+  </si>
+  <si>
+    <t>show</t>
+  </si>
+  <si>
+    <t>演出</t>
+  </si>
+  <si>
+    <t>{"statsSumAtLeast":240}</t>
+  </si>
+  <si>
+    <t>灯亮起来的那一刻，全场安静了。（粉丝 +300 · 收入 +1500）</t>
+  </si>
+  <si>
+    <t>res-show-a</t>
+  </si>
+  <si>
+    <t>{"statsSumAtLeast":180}</t>
+  </si>
+  <si>
+    <t>发挥很稳，台下有人跟着喊。（粉丝 +180 · 收入 +900）</t>
+  </si>
+  <si>
+    <t>res-show-b</t>
+  </si>
+  <si>
+    <t>{"statsSumAtLeast":120}</t>
+  </si>
+  <si>
+    <t>中规中矩，但没出错。（粉丝 +100 · 收入 +500）</t>
+  </si>
+  <si>
+    <t>res-show-c</t>
+  </si>
+  <si>
+    <t>中间忘了一个动作，你笑着圆过去了。（粉丝 +40 · 收入 +200）</t>
   </si>
 </sst>
 </file>
@@ -540,16 +582,16 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:L10"/>
+  <dimension ref="A1:M14"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="4" width="18" customWidth="1"/>
     <col min="5" max="5" width="16" customWidth="1"/>
-    <col min="6" max="11" width="14" customWidth="1"/>
-    <col min="12" max="12" width="18" customWidth="1"/>
+    <col min="6" max="12" width="14" customWidth="1"/>
+    <col min="13" max="13" width="18" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:12" s="1" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:13" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -586,19 +628,22 @@
       <c r="L1" s="1" t="s">
         <v>11</v>
       </c>
-    </row>
-    <row r="2" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="M1" s="1" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="2" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="B2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="C2" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="D2" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="E2">
         <v>99</v>
@@ -613,30 +658,33 @@
         <v>16</v>
       </c>
       <c r="I2" t="s">
+        <v>17</v>
+      </c>
+      <c r="J2" t="s">
+        <v>16</v>
+      </c>
+      <c r="K2" t="s">
+        <v>16</v>
+      </c>
+      <c r="L2" t="s">
+        <v>16</v>
+      </c>
+      <c r="M2" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="3" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
+        <v>19</v>
+      </c>
+      <c r="B3" t="s">
+        <v>14</v>
+      </c>
+      <c r="C3" t="s">
         <v>15</v>
       </c>
-      <c r="J2" t="s">
-        <v>15</v>
-      </c>
-      <c r="K2" t="s">
-        <v>15</v>
-      </c>
-      <c r="L2" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="3" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A3" t="s">
-        <v>18</v>
-      </c>
-      <c r="B3" t="s">
-        <v>13</v>
-      </c>
-      <c r="C3" t="s">
-        <v>14</v>
-      </c>
       <c r="D3" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="E3">
         <v>10</v>
@@ -648,33 +696,36 @@
         <v>-50</v>
       </c>
       <c r="H3" t="s">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="I3" t="s">
-        <v>15</v>
+        <v>21</v>
       </c>
       <c r="J3" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="K3" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="L3" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="4" spans="1:12" x14ac:dyDescent="0.25">
+        <v>16</v>
+      </c>
+      <c r="M3" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="4" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="B4" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="C4" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="D4" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="E4">
         <v>99</v>
@@ -683,36 +734,39 @@
         <v>-12</v>
       </c>
       <c r="G4" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="H4" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="I4" t="s">
         <v>16</v>
       </c>
       <c r="J4" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="K4" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="L4" t="s">
+        <v>16</v>
+      </c>
+      <c r="M4" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="5" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A5" t="s">
+        <v>27</v>
+      </c>
+      <c r="B5" t="s">
+        <v>24</v>
+      </c>
+      <c r="C5" t="s">
         <v>25</v>
       </c>
-    </row>
-    <row r="5" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A5" t="s">
-        <v>26</v>
-      </c>
-      <c r="B5" t="s">
-        <v>23</v>
-      </c>
-      <c r="C5" t="s">
-        <v>24</v>
-      </c>
       <c r="D5" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="E5">
         <v>10</v>
@@ -721,36 +775,39 @@
         <v>-12</v>
       </c>
       <c r="G5" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="H5" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="I5" t="s">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="J5" t="s">
-        <v>15</v>
+        <v>21</v>
       </c>
       <c r="K5" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="L5" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="6" spans="1:12" x14ac:dyDescent="0.25">
+        <v>16</v>
+      </c>
+      <c r="M5" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="6" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="B6" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="C6" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="D6" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="E6">
         <v>99</v>
@@ -759,36 +816,39 @@
         <v>-10</v>
       </c>
       <c r="G6" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="H6" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="I6" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="J6" t="s">
-        <v>32</v>
+        <v>16</v>
       </c>
       <c r="K6" t="s">
-        <v>15</v>
+        <v>33</v>
       </c>
       <c r="L6" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="7" spans="1:12" x14ac:dyDescent="0.25">
+        <v>16</v>
+      </c>
+      <c r="M6" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="7" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="B7" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="C7" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="D7" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="E7">
         <v>99</v>
@@ -797,36 +857,39 @@
         <v>-8</v>
       </c>
       <c r="G7" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="H7" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="I7" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="J7" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="K7" t="s">
-        <v>32</v>
+        <v>16</v>
       </c>
       <c r="L7" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="8" spans="1:12" x14ac:dyDescent="0.25">
+        <v>33</v>
+      </c>
+      <c r="M7" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="8" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="B8" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="C8" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="D8" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="E8">
         <v>99</v>
@@ -838,33 +901,36 @@
         <v>320</v>
       </c>
       <c r="H8" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="I8" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="J8" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="K8" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="L8" t="s">
+        <v>16</v>
+      </c>
+      <c r="M8" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="9" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A9" t="s">
+        <v>43</v>
+      </c>
+      <c r="B9" t="s">
+        <v>40</v>
+      </c>
+      <c r="C9" t="s">
         <v>41</v>
       </c>
-    </row>
-    <row r="9" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A9" t="s">
-        <v>42</v>
-      </c>
-      <c r="B9" t="s">
-        <v>39</v>
-      </c>
-      <c r="C9" t="s">
-        <v>40</v>
-      </c>
       <c r="D9" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="E9">
         <v>10</v>
@@ -876,33 +942,36 @@
         <v>240</v>
       </c>
       <c r="H9" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="I9" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="J9" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="K9" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="L9" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="10" spans="1:12" x14ac:dyDescent="0.25">
+        <v>16</v>
+      </c>
+      <c r="M9" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="10" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="B10" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="C10" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="D10" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="E10">
         <v>99</v>
@@ -911,22 +980,189 @@
         <v>25</v>
       </c>
       <c r="G10" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="H10" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="I10" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="J10" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="K10" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="L10" t="s">
-        <v>47</v>
+        <v>16</v>
+      </c>
+      <c r="M10" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="11" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A11" t="s">
+        <v>49</v>
+      </c>
+      <c r="B11" t="s">
+        <v>50</v>
+      </c>
+      <c r="C11" t="s">
+        <v>51</v>
+      </c>
+      <c r="D11" t="s">
+        <v>52</v>
+      </c>
+      <c r="E11">
+        <v>10</v>
+      </c>
+      <c r="F11">
+        <v>-30</v>
+      </c>
+      <c r="G11">
+        <v>1500</v>
+      </c>
+      <c r="H11">
+        <v>300</v>
+      </c>
+      <c r="I11" t="s">
+        <v>16</v>
+      </c>
+      <c r="J11" t="s">
+        <v>16</v>
+      </c>
+      <c r="K11" t="s">
+        <v>16</v>
+      </c>
+      <c r="L11" t="s">
+        <v>16</v>
+      </c>
+      <c r="M11" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="12" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A12" t="s">
+        <v>54</v>
+      </c>
+      <c r="B12" t="s">
+        <v>50</v>
+      </c>
+      <c r="C12" t="s">
+        <v>51</v>
+      </c>
+      <c r="D12" t="s">
+        <v>55</v>
+      </c>
+      <c r="E12">
+        <v>20</v>
+      </c>
+      <c r="F12">
+        <v>-30</v>
+      </c>
+      <c r="G12">
+        <v>900</v>
+      </c>
+      <c r="H12">
+        <v>180</v>
+      </c>
+      <c r="I12" t="s">
+        <v>16</v>
+      </c>
+      <c r="J12" t="s">
+        <v>16</v>
+      </c>
+      <c r="K12" t="s">
+        <v>16</v>
+      </c>
+      <c r="L12" t="s">
+        <v>16</v>
+      </c>
+      <c r="M12" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="13" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A13" t="s">
+        <v>57</v>
+      </c>
+      <c r="B13" t="s">
+        <v>50</v>
+      </c>
+      <c r="C13" t="s">
+        <v>51</v>
+      </c>
+      <c r="D13" t="s">
+        <v>58</v>
+      </c>
+      <c r="E13">
+        <v>30</v>
+      </c>
+      <c r="F13">
+        <v>-30</v>
+      </c>
+      <c r="G13">
+        <v>500</v>
+      </c>
+      <c r="H13">
+        <v>100</v>
+      </c>
+      <c r="I13" t="s">
+        <v>16</v>
+      </c>
+      <c r="J13" t="s">
+        <v>16</v>
+      </c>
+      <c r="K13" t="s">
+        <v>16</v>
+      </c>
+      <c r="L13" t="s">
+        <v>16</v>
+      </c>
+      <c r="M13" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="14" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A14" t="s">
+        <v>60</v>
+      </c>
+      <c r="B14" t="s">
+        <v>50</v>
+      </c>
+      <c r="C14" t="s">
+        <v>51</v>
+      </c>
+      <c r="D14" t="s">
+        <v>16</v>
+      </c>
+      <c r="E14">
+        <v>99</v>
+      </c>
+      <c r="F14">
+        <v>-30</v>
+      </c>
+      <c r="G14">
+        <v>200</v>
+      </c>
+      <c r="H14">
+        <v>40</v>
+      </c>
+      <c r="I14" t="s">
+        <v>16</v>
+      </c>
+      <c r="J14" t="s">
+        <v>16</v>
+      </c>
+      <c r="K14" t="s">
+        <v>16</v>
+      </c>
+      <c r="L14" t="s">
+        <v>16</v>
+      </c>
+      <c r="M14" t="s">
+        <v>61</v>
       </c>
     </row>
   </sheetData>
